--- a/backend/static/site/files/child_import_template.xlsx
+++ b/backend/static/site/files/child_import_template.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -643,6 +643,50 @@
       <c r="D11" s="3" t="inlineStr">
         <is>
           <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Направление</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Текст. НЕ создаётся автоматически — сухой прогон предупредит, если такого направления ещё нет в справочнике</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Балет</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Группа</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Текст. НЕ создаётся автоматически — сухой прогон предупредит, если такой группы ещё нет</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Балет-мини вторник/четверг</t>
         </is>
       </c>
     </row>
@@ -657,7 +701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -668,6 +712,8 @@
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="26" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -711,6 +757,16 @@
           <t>Остаток занятий</t>
         </is>
       </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Направление</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Группа</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -745,6 +801,16 @@
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Балет</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Балет-мини вторник/четверг</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -783,6 +849,8 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
